--- a/교부확인서_샘플.xlsx
+++ b/교부확인서_샘플.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtinet\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871B9BF7-86A3-4E28-93C1-30F5D0218EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EABE78-FCB9-4741-A838-49040D5D5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="885" yWindow="6465" windowWidth="19530" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>학교명</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>B100000001</t>
-  </si>
-  <si>
-    <t>2026년 글로벌 현장학습</t>
   </si>
   <si>
     <t>2026-04-01</t>
@@ -65,6 +62,14 @@
   </si>
   <si>
     <t>B100000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssafasf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,54 +490,54 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1">
         <v>5000000</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>4500000</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1">
         <v>6500000</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A3:C3 E3 A2:C2 E2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A3:B3 E3 A2:B2 E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/교부확인서_샘플.xlsx
+++ b/교부확인서_샘플.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtinet\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EABE78-FCB9-4741-A838-49040D5D5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83672AA9-171B-43B3-9A6C-CD14AD09BE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="885" yWindow="6465" windowWidth="19530" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>학교명</t>
   </si>
@@ -65,11 +65,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssafasf</t>
+    <t>2025 글로벌 현장학습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,7 +520,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>6500000</v>
